--- a/inst/extdata/SHMI_template.xlsx
+++ b/inst/extdata/SHMI_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myRpackages\SHMI\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792F3074-56B3-4216-A3CA-F4A9CD3EAC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{066CDBA5-9BCD-4C23-9AA0-F4ED3207F345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27405" yWindow="315" windowWidth="21600" windowHeight="15075" tabRatio="836" xr2:uid="{DDAFFBF6-EAD5-488B-844A-6854A073B0F1}"/>
+    <workbookView xWindow="-27915" yWindow="90" windowWidth="22020" windowHeight="15450" tabRatio="836" activeTab="6" xr2:uid="{DDAFFBF6-EAD5-488B-844A-6854A073B0F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="13" r:id="rId1"/>
@@ -381,7 +381,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="660">
   <si>
     <t>Description</t>
   </si>
@@ -2196,12 +2196,6 @@
   </si>
   <si>
     <t>SA_K2O</t>
-  </si>
-  <si>
-    <t>SuperU</t>
-  </si>
-  <si>
-    <t>surface banded urea</t>
   </si>
   <si>
     <t>MLSH</t>
@@ -3468,7 +3462,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="56" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="18" x14ac:dyDescent="0.25">
@@ -3476,12 +3470,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="57" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -3489,12 +3483,12 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="59" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="60" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -3502,12 +3496,12 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="59" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="60" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -3515,32 +3509,32 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="59" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="61" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="61" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="60" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="60" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="60" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -3548,32 +3542,32 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="59" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="60" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="60" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="60" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="60" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="60" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -3581,17 +3575,17 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="59" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="60" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="60" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -3599,17 +3593,17 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="59" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="60" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="60" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -4741,10 +4735,10 @@
         <v>512</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="H1" s="25" t="s">
         <v>515</v>
@@ -4817,13 +4811,13 @@
         <v>8</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -8135,7 +8129,7 @@
         <v>24</v>
       </c>
       <c r="K1" s="25" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L1" s="25" t="s">
         <v>23</v>
@@ -25560,10 +25554,10 @@
         <v>525</v>
       </c>
       <c r="I1" s="25" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="J1" s="25" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="K1" s="25" t="s">
         <v>523</v>
@@ -25639,13 +25633,13 @@
         <v>507</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="K3" s="22" t="s">
         <v>40</v>
@@ -25782,9 +25776,7 @@
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
-      <c r="M10" s="8" t="s">
-        <v>604</v>
-      </c>
+      <c r="M10" s="8"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
@@ -25799,9 +25791,7 @@
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
-      <c r="M11" s="8" t="s">
-        <v>604</v>
-      </c>
+      <c r="M11" s="8"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
@@ -25816,9 +25806,7 @@
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
-      <c r="M12" s="8" t="s">
-        <v>604</v>
-      </c>
+      <c r="M12" s="8"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
@@ -25833,9 +25821,7 @@
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
-      <c r="M13" s="8" t="s">
-        <v>604</v>
-      </c>
+      <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
@@ -25850,9 +25836,7 @@
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
-      <c r="M14" s="8" t="s">
-        <v>604</v>
-      </c>
+      <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
@@ -25942,9 +25926,7 @@
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
-      <c r="M20" s="8" t="s">
-        <v>604</v>
-      </c>
+      <c r="M20" s="8"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
@@ -25959,9 +25941,7 @@
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
-      <c r="M21" s="8" t="s">
-        <v>604</v>
-      </c>
+      <c r="M21" s="8"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
@@ -25976,9 +25956,7 @@
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
-      <c r="M22" s="8" t="s">
-        <v>604</v>
-      </c>
+      <c r="M22" s="8"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
@@ -25993,9 +25971,7 @@
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
-      <c r="M23" s="8" t="s">
-        <v>604</v>
-      </c>
+      <c r="M23" s="8"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
@@ -26010,9 +25986,7 @@
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
-      <c r="M24" s="8" t="s">
-        <v>604</v>
-      </c>
+      <c r="M24" s="8"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
@@ -26027,9 +26001,7 @@
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
-      <c r="M25" s="8" t="s">
-        <v>605</v>
-      </c>
+      <c r="M25" s="8"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
@@ -26044,9 +26016,7 @@
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
-      <c r="M26" s="8" t="s">
-        <v>605</v>
-      </c>
+      <c r="M26" s="8"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
@@ -26061,9 +26031,7 @@
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
-      <c r="M27" s="8" t="s">
-        <v>605</v>
-      </c>
+      <c r="M27" s="8"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
@@ -26078,9 +26046,7 @@
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
-      <c r="M28" s="8" t="s">
-        <v>605</v>
-      </c>
+      <c r="M28" s="8"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
@@ -26095,9 +26061,7 @@
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
-      <c r="M29" s="8" t="s">
-        <v>605</v>
-      </c>
+      <c r="M29" s="8"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
@@ -26112,9 +26076,7 @@
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
-      <c r="M30" s="8" t="s">
-        <v>605</v>
-      </c>
+      <c r="M30" s="8"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
@@ -26129,9 +26091,7 @@
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
-      <c r="M31" s="8" t="s">
-        <v>605</v>
-      </c>
+      <c r="M31" s="8"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
@@ -26146,9 +26106,7 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
-      <c r="M32" s="8" t="s">
-        <v>605</v>
-      </c>
+      <c r="M32" s="8"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
@@ -26163,9 +26121,7 @@
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
-      <c r="M33" s="8" t="s">
-        <v>605</v>
-      </c>
+      <c r="M33" s="8"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
@@ -26180,9 +26136,7 @@
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
-      <c r="M34" s="8" t="s">
-        <v>605</v>
-      </c>
+      <c r="M34" s="8"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
@@ -26197,9 +26151,7 @@
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
-      <c r="M35" s="8" t="s">
-        <v>605</v>
-      </c>
+      <c r="M35" s="8"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
@@ -26214,9 +26166,7 @@
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
-      <c r="M36" s="8" t="s">
-        <v>605</v>
-      </c>
+      <c r="M36" s="8"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
@@ -26231,9 +26181,7 @@
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
-      <c r="M37" s="8" t="s">
-        <v>605</v>
-      </c>
+      <c r="M37" s="8"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
@@ -26248,9 +26196,7 @@
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
-      <c r="M38" s="8" t="s">
-        <v>605</v>
-      </c>
+      <c r="M38" s="8"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
@@ -26265,9 +26211,7 @@
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
-      <c r="M39" s="8" t="s">
-        <v>605</v>
-      </c>
+      <c r="M39" s="8"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
@@ -38961,10 +38905,10 @@
         <v>508</v>
       </c>
       <c r="F1" s="50" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="G1" s="50" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H1" s="50" t="s">
         <v>505</v>
@@ -39067,10 +39011,10 @@
         <v>538</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>539</v>
@@ -46283,7 +46227,7 @@
         <v>442</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="AP1" s="1" t="s">
         <v>431</v>
@@ -46292,7 +46236,7 @@
         <v>432</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="2" spans="1:44" x14ac:dyDescent="0.25">
@@ -46426,7 +46370,7 @@
         <v>355</v>
       </c>
       <c r="AR2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.25">
@@ -46551,7 +46495,7 @@
         <v>348</v>
       </c>
       <c r="AO3" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AP3" t="s">
         <v>203</v>
@@ -46560,7 +46504,7 @@
         <v>354</v>
       </c>
       <c r="AR3" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.25">
@@ -46692,7 +46636,7 @@
         <v>353</v>
       </c>
       <c r="AR4" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.25">
@@ -46805,7 +46749,7 @@
         <v>69</v>
       </c>
       <c r="AO5" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AP5" t="s">
         <v>108</v>
@@ -46814,7 +46758,7 @@
         <v>352</v>
       </c>
       <c r="AR5" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.25">
@@ -46918,7 +46862,7 @@
         <v>119</v>
       </c>
       <c r="AR6" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.25">
@@ -47016,7 +46960,7 @@
         <v>71</v>
       </c>
       <c r="AR7" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.25">
@@ -47024,7 +46968,7 @@
         <v>131</v>
       </c>
       <c r="B8" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="G8" t="s">
         <v>52</v>
@@ -47108,7 +47052,7 @@
         <v>83</v>
       </c>
       <c r="AR8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.25">
@@ -47116,7 +47060,7 @@
         <v>141</v>
       </c>
       <c r="B9" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="G9" t="s">
         <v>435</v>
@@ -47188,7 +47132,7 @@
         <v>405</v>
       </c>
       <c r="AR9" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.25">
@@ -47259,7 +47203,7 @@
         <v>406</v>
       </c>
       <c r="AR10" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.25">
@@ -47321,7 +47265,7 @@
         <v>191</v>
       </c>
       <c r="AR11" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.25">
@@ -47374,7 +47318,7 @@
         <v>161</v>
       </c>
       <c r="AR12" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.25">
@@ -47424,7 +47368,7 @@
         <v>130</v>
       </c>
       <c r="AR13" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.25">
